--- a/ky/downloads/data-excel/2.3.2.b.xlsx
+++ b/ky/downloads/data-excel/2.3.2.b.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B75B64C-0A0A-4B98-A5EB-3AEDD7A4B16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2.3.3.1.с" sheetId="2" r:id="rId1"/>
+    <sheet name="2.3.2.b" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -17,7 +18,7 @@
     <definedName name="CL_REF_AREA_DESCRIPTION">[1]VAL_CL_AREA!$A$2:$B$573</definedName>
     <definedName name="CL_SERIES_DESCRIPTION">[1]VAL_CL_SDG_SERIES!$A$2:$B$312</definedName>
     <definedName name="CL_UNIT_MEASURE_DESCRIPTION">[1]VAL_CL_UNIT!$A$2:$B$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.3.3.1.с'!$B$1:$O$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.3.2.b'!$B$1:$O$9</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -25,9 +26,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t xml:space="preserve">2.3.3.1c Баланс потребления рыбной продукции на душу населения </t>
-  </si>
   <si>
     <t>Потребление рыбной продукции на душу насления  (кг/год)</t>
   </si>
@@ -44,25 +42,28 @@
     <t>Items</t>
   </si>
   <si>
-    <t>2.3.3.1c Balance of fishery consumption per capita</t>
-  </si>
-  <si>
     <t>(kilogram)</t>
   </si>
   <si>
     <t>Consumption of fish products per capita (kg/year)</t>
   </si>
   <si>
-    <t>2.3.3.1c Калктын башына балык чарбачылыгын керектөө балансы</t>
+    <t>Калктын башына балык азыктарын керектөө (кг/жылына)</t>
   </si>
   <si>
-    <t>Калктын башына балык азыктарын керектөө (кг/жылына)</t>
+    <t>2.3.2.b Калктын башына балык чарбачылыгын керектөө балансы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3.2.b Баланс потребления рыбной продукции на душу населения </t>
+  </si>
+  <si>
+    <t>2.3.2.b Balance of fishery consumption per capita</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -215,24 +216,21 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -247,13 +245,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -265,22 +260,22 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Normal 17" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -296,7 +291,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -7761,9 +7756,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7801,9 +7796,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7838,7 +7833,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7873,7 +7868,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8046,26 +8041,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="37.7109375" style="5" customWidth="1"/>
-    <col min="4" max="13" width="9.140625" style="5"/>
-    <col min="14" max="14" width="6.85546875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="8" style="5" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="3" width="37.7109375" style="4" customWidth="1"/>
+    <col min="4" max="13" width="9.140625" style="4"/>
+    <col min="14" max="14" width="6.85546875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="8" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
@@ -8079,547 +8074,197 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>2</v>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>2</v>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>7</v>
+      <c r="C2" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>2010</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>2011</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>2012</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>2013</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>2014</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>2015</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>2016</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="11">
         <v>2017</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="11">
         <v>2018</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="11">
         <v>2019</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="11">
         <v>2020</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="11">
         <v>2021</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="11">
         <v>2022</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="11">
         <v>2023</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="R4" s="11">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>10</v>
+    <row r="5" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>7</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="F5" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="G5" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="H5" s="14">
+        <v>1.9</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="K5" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="N5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="E5" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="H5" s="16">
-        <v>1.9</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="J5" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="K5" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="L5" s="15">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="N5" s="15">
-        <v>1</v>
-      </c>
-      <c r="O5" s="15">
+      <c r="O5" s="13">
         <v>1.4</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="13">
         <v>3</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="13">
         <v>4.8</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="R5" s="13">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
